--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-15.xlsx
@@ -65,103 +65,103 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>57</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>45</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>16,885,105,340.4</t>
-  </si>
-  <si>
-    <t>1,040,062,576.84</t>
-  </si>
-  <si>
-    <t>908,671,751.69</t>
-  </si>
-  <si>
-    <t>660,750,686.45</t>
-  </si>
-  <si>
-    <t>602,196,906.69</t>
-  </si>
-  <si>
-    <t>556,275,329.79</t>
-  </si>
-  <si>
-    <t>548,688,941.28</t>
-  </si>
-  <si>
-    <t>8,457,036,952.0</t>
-  </si>
-  <si>
-    <t>521,671,237.4</t>
-  </si>
-  <si>
-    <t>250,190,673.29</t>
-  </si>
-  <si>
-    <t>226,153,501.2</t>
-  </si>
-  <si>
-    <t>285,206,761.0</t>
-  </si>
-  <si>
-    <t>273,928,174.6</t>
-  </si>
-  <si>
-    <t>355,927,275.68</t>
-  </si>
-  <si>
-    <t>8,428,068,388.4</t>
-  </si>
-  <si>
-    <t>518,391,339.45</t>
-  </si>
-  <si>
-    <t>658,481,078.4</t>
-  </si>
-  <si>
-    <t>434,597,185.25</t>
-  </si>
-  <si>
-    <t>316,990,145.69</t>
-  </si>
-  <si>
-    <t>282,347,155.2</t>
-  </si>
-  <si>
-    <t>192,761,665.6</t>
+    <t>1,128,866,294.5</t>
+  </si>
+  <si>
+    <t>853,459,532.45</t>
+  </si>
+  <si>
+    <t>663,316,301.29</t>
+  </si>
+  <si>
+    <t>585,251,367.79</t>
+  </si>
+  <si>
+    <t>569,393,930.1</t>
+  </si>
+  <si>
+    <t>565,304,264.28</t>
+  </si>
+  <si>
+    <t>538,725,363.95</t>
+  </si>
+  <si>
+    <t>515,851,077.0</t>
+  </si>
+  <si>
+    <t>513,931,585.7</t>
+  </si>
+  <si>
+    <t>296,574,446.1</t>
+  </si>
+  <si>
+    <t>294,696,364.1</t>
+  </si>
+  <si>
+    <t>440,711,608.1</t>
+  </si>
+  <si>
+    <t>312,144,762.88</t>
+  </si>
+  <si>
+    <t>315,711,535.7</t>
+  </si>
+  <si>
+    <t>613,015,217.5</t>
+  </si>
+  <si>
+    <t>339,527,946.75</t>
+  </si>
+  <si>
+    <t>366,741,855.19</t>
+  </si>
+  <si>
+    <t>290,555,003.7</t>
+  </si>
+  <si>
+    <t>128,682,322.0</t>
+  </si>
+  <si>
+    <t>253,159,501.4</t>
+  </si>
+  <si>
+    <t>223,013,828.25</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,487 +182,484 @@
     <t>UPPER</t>
   </si>
   <si>
-    <t>8,188,558,771.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>39,274,193.0</t>
+    <t>231,197,843.0</t>
   </si>
   <si>
     <t>SPIL</t>
   </si>
   <si>
-    <t>28,329,309.4</t>
+    <t>32,840,724.79</t>
   </si>
   <si>
     <t>SBI</t>
   </si>
   <si>
-    <t>27,233,988.8</t>
+    <t>28,894,488.8</t>
   </si>
   <si>
     <t>MSLB</t>
   </si>
   <si>
-    <t>24,354,516.6</t>
+    <t>24,368,217.6</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>19,244,699.39</t>
+  </si>
+  <si>
+    <t>112,109,050.2</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>119,921,239.5</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>97,559,699.4</t>
-  </si>
-  <si>
-    <t>SINDU</t>
-  </si>
-  <si>
-    <t>34,977,020.0</t>
-  </si>
-  <si>
-    <t>GMFBS</t>
-  </si>
-  <si>
-    <t>27,953,333.3</t>
+    <t>61,516,028.6</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>30,495,631.1</t>
   </si>
   <si>
     <t>LBBL</t>
   </si>
   <si>
-    <t>16,274,528.6</t>
+    <t>14,811,312.8</t>
+  </si>
+  <si>
+    <t>MMKJL</t>
+  </si>
+  <si>
+    <t>12,876,799.1</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>19,099,272.6</t>
+  </si>
+  <si>
+    <t>16,597,907.6</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>11,252,966.5</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>10,480,450.0</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>6,901,011.0</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>36,150,960.2</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>30,904,723.4</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>15,790,498.0</t>
+  </si>
+  <si>
+    <t>GBILD84/85</t>
+  </si>
+  <si>
+    <t>11,720,000.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>10,838,176.5</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>165,327,387.19</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>150,270,816.8</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>11,194,830.0</t>
+  </si>
+  <si>
+    <t>8,363,960.0</t>
+  </si>
+  <si>
+    <t>5,587,190.0</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>13,870,334.39</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>11,472,997.0</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>8,904,782.8</t>
+  </si>
+  <si>
+    <t>KPCL</t>
+  </si>
+  <si>
+    <t>8,864,835.19</t>
+  </si>
+  <si>
+    <t>8,527,395.19</t>
+  </si>
+  <si>
+    <t>NICL</t>
+  </si>
+  <si>
+    <t>65,056,384.6</t>
+  </si>
+  <si>
+    <t>MHNL</t>
+  </si>
+  <si>
+    <t>14,119,140.0</t>
+  </si>
+  <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>10,842,151.5</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>8,867,971.5</t>
+  </si>
+  <si>
+    <t>8,863,176.19</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>243,740,807.0</t>
+  </si>
+  <si>
+    <t>38,092,842.29</t>
+  </si>
+  <si>
+    <t>36,999,976.2</t>
+  </si>
+  <si>
+    <t>31,323,602.2</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>27,366,826.3</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>47,318,562.6</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>20,505,391.39</t>
   </si>
   <si>
     <t>SIFC</t>
   </si>
   <si>
-    <t>24,234,050.0</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>21,705,564.0</t>
+    <t>14,745,552.7</t>
+  </si>
+  <si>
+    <t>9,129,551.0</t>
+  </si>
+  <si>
+    <t>NWCL</t>
+  </si>
+  <si>
+    <t>8,711,057.0</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>24,090,049.6</t>
   </si>
   <si>
     <t>HDL</t>
   </si>
   <si>
-    <t>15,639,813.5</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>14,679,081.6</t>
+    <t>21,847,024.0</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>18,092,929.8</t>
+  </si>
+  <si>
+    <t>14,597,753.1</t>
+  </si>
+  <si>
+    <t>MERO</t>
+  </si>
+  <si>
+    <t>13,875,261.4</t>
+  </si>
+  <si>
+    <t>26,553,960.7</t>
+  </si>
+  <si>
+    <t>GLH</t>
+  </si>
+  <si>
+    <t>19,354,624.0</t>
+  </si>
+  <si>
+    <t>SLBSL</t>
+  </si>
+  <si>
+    <t>14,245,605.0</t>
+  </si>
+  <si>
+    <t>11,154,880.0</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>11,036,847.1</t>
+  </si>
+  <si>
+    <t>23,821,477.5</t>
+  </si>
+  <si>
+    <t>PRVUPO</t>
+  </si>
+  <si>
+    <t>13,388,700.0</t>
+  </si>
+  <si>
+    <t>UNL</t>
+  </si>
+  <si>
+    <t>12,464,701.1</t>
+  </si>
+  <si>
+    <t>10,454,036.5</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>9,205,215.1</t>
+  </si>
+  <si>
+    <t>25,260,676.1</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>9,681,701.1</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>7,900,839.0</t>
+  </si>
+  <si>
+    <t>7,135,516.3</t>
+  </si>
+  <si>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>6,445,241.0</t>
+  </si>
+  <si>
+    <t>14,849,381.0</t>
+  </si>
+  <si>
+    <t>8,522,921.3</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>8,467,899.6</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>7,323,750.0</t>
+  </si>
+  <si>
+    <t>7,086,178.2</t>
+  </si>
+  <si>
+    <t>Top Traded Stocks</t>
+  </si>
+  <si>
+    <t>Turnover (Rs.)</t>
+  </si>
+  <si>
+    <t>Sub Indices</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Percentage (%)</t>
+  </si>
+  <si>
+    <t>354,523,738.9</t>
+  </si>
+  <si>
+    <t>253,124,714.5</t>
+  </si>
+  <si>
+    <t>224,284,500.0</t>
+  </si>
+  <si>
+    <t>189,862,991.6</t>
   </si>
   <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>11,893,374.5</t>
-  </si>
-  <si>
-    <t>AVYAN</t>
-  </si>
-  <si>
-    <t>35,088,410.0</t>
-  </si>
-  <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>14,376,143.7</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>10,775,888.3</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>10,467,502.6</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>7,187,043.9</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>54,772,583.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>10,253,963.5</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>9,495,617.6</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>9,300,150.79</t>
-  </si>
-  <si>
-    <t>8,396,344.6</t>
-  </si>
-  <si>
-    <t>32,852,328.5</t>
-  </si>
-  <si>
-    <t>CIT</t>
-  </si>
-  <si>
-    <t>17,344,215.0</t>
-  </si>
-  <si>
-    <t>MKHC</t>
-  </si>
-  <si>
-    <t>17,184,332.0</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>17,082,490.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>12,764,453.2</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>47,271,887.2</t>
-  </si>
-  <si>
-    <t>HHL</t>
-  </si>
-  <si>
-    <t>22,250,997.0</t>
-  </si>
-  <si>
-    <t>19,176,456.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>19,051,275.0</t>
-  </si>
-  <si>
-    <t>17,154,324.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>8,197,768,107.2</t>
-  </si>
-  <si>
-    <t>31,405,892.5</t>
-  </si>
-  <si>
-    <t>25,617,208.1</t>
-  </si>
-  <si>
-    <t>24,372,196.6</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>13,876,024.0</t>
-  </si>
-  <si>
-    <t>72,663,034.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>32,860,097.1</t>
-  </si>
-  <si>
-    <t>31,381,326.7</t>
-  </si>
-  <si>
-    <t>31,220,255.4</t>
-  </si>
-  <si>
-    <t>24,467,373.8</t>
-  </si>
-  <si>
-    <t>238,529,406.5</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>81,143,715.3</t>
-  </si>
-  <si>
-    <t>50,334,532.2</t>
-  </si>
-  <si>
-    <t>BBC</t>
-  </si>
-  <si>
-    <t>38,800,000.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>26,587,751.3</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>55,815,146.0</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>41,763,277.79</t>
-  </si>
-  <si>
-    <t>36,921,020.0</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>25,447,792.8</t>
-  </si>
-  <si>
-    <t>GILB</t>
-  </si>
-  <si>
-    <t>24,277,892.9</t>
-  </si>
-  <si>
-    <t>NUBL</t>
-  </si>
-  <si>
-    <t>17,425,590.0</t>
-  </si>
-  <si>
-    <t>PPCL</t>
-  </si>
-  <si>
-    <t>14,198,990.0</t>
-  </si>
-  <si>
-    <t>13,375,808.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>12,686,006.5</t>
-  </si>
-  <si>
-    <t>MERO</t>
-  </si>
-  <si>
-    <t>11,491,518.9</t>
-  </si>
-  <si>
-    <t>83,746,702.0</t>
-  </si>
-  <si>
-    <t>34,096,482.0</t>
-  </si>
-  <si>
-    <t>CZBIL</t>
-  </si>
-  <si>
-    <t>11,500,614.0</t>
-  </si>
-  <si>
-    <t>9,133,160.9</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>7,160,616.1</t>
-  </si>
-  <si>
-    <t>NWCL</t>
-  </si>
-  <si>
-    <t>10,708,384.1</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>9,681,701.1</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>7,192,711.4</t>
-  </si>
-  <si>
-    <t>6,488,659.9</t>
-  </si>
-  <si>
-    <t>GMFIL</t>
-  </si>
-  <si>
-    <t>5,819,327.0</t>
-  </si>
-  <si>
-    <t>Top Traded Stocks</t>
-  </si>
-  <si>
-    <t>Turnover (Rs.)</t>
-  </si>
-  <si>
-    <t>Sub Indices</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Percentage (%)</t>
-  </si>
-  <si>
-    <t>8,297,635,679.9</t>
-  </si>
-  <si>
-    <t>253,764,452.1</t>
-  </si>
-  <si>
-    <t>202,403,148.9</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>199,858,383.2</t>
-  </si>
-  <si>
-    <t>181,664,294.4</t>
+    <t>155,864,343.5</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>10,189,006,628.79</t>
+    <t>2,371,978,612.0</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,793,522,985.05</t>
+    <t>2,026,556,250.15</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>814,358,838.6</t>
+    <t>958,634,388.4</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>769,199,847.7</t>
+    <t>623,828,484.2</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>561,928,464.2</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>530,021,262.5</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>647,584,541.2</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>629,238,781.4</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>536,707,699.7</t>
+    <t>387,703,796.8</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>293,989,458.0</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>325,642,453.7</t>
+    <t>270,835,594.2</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>165,146,852.0</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>164,699,354.4</t>
+    <t>198,403,725.7</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>69,681,029.4</t>
+    <t>65,452,981.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>41,818,386.79</t>
+    <t>54,955,664.5</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>22,718,610.5</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>16,844,730.19</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>39,705,640.0</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>12,543,582.0</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>10,122,923.84</t>
+    <t>1,746,285.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -674,211 +671,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>8,205,973,346.3</t>
-  </si>
-  <si>
-    <t>127,279,587.2</t>
-  </si>
-  <si>
-    <t>35,821,869.9</t>
-  </si>
-  <si>
-    <t>30,306,356.9</t>
-  </si>
-  <si>
-    <t>19,350,879.2</t>
-  </si>
-  <si>
-    <t>175,609,598.8</t>
-  </si>
-  <si>
-    <t>164,838,567.4</t>
-  </si>
-  <si>
-    <t>65,686,648.5</t>
-  </si>
-  <si>
-    <t>39,214,872.0</t>
-  </si>
-  <si>
-    <t>38,154,705.4</t>
-  </si>
-  <si>
-    <t>53,104,102.6</t>
-  </si>
-  <si>
-    <t>50,473,055.1</t>
-  </si>
-  <si>
-    <t>49,594,442.7</t>
-  </si>
-  <si>
-    <t>25,365,080.0</t>
-  </si>
-  <si>
-    <t>21,115,537.89</t>
-  </si>
-  <si>
-    <t>61,427,508.4</t>
-  </si>
-  <si>
-    <t>45,284,331.0</t>
-  </si>
-  <si>
-    <t>41,476,242.7</t>
-  </si>
-  <si>
-    <t>20,503,613.2</t>
-  </si>
-  <si>
-    <t>17,692,292.39</t>
-  </si>
-  <si>
-    <t>64,982,513.2</t>
-  </si>
-  <si>
-    <t>64,227,439.45</t>
-  </si>
-  <si>
-    <t>53,799,010.5</t>
-  </si>
-  <si>
-    <t>23,179,563.0</t>
-  </si>
-  <si>
-    <t>21,284,066.89</t>
-  </si>
-  <si>
-    <t>107,393,776.8</t>
-  </si>
-  <si>
-    <t>34,106,934.4</t>
-  </si>
-  <si>
-    <t>34,056,607.7</t>
-  </si>
-  <si>
-    <t>31,897,846.2</t>
-  </si>
-  <si>
-    <t>27,226,182.5</t>
-  </si>
-  <si>
-    <t>140,266,542.9</t>
-  </si>
-  <si>
-    <t>73,584,350.9</t>
-  </si>
-  <si>
-    <t>42,587,386.0</t>
-  </si>
-  <si>
-    <t>26,765,672.8</t>
-  </si>
-  <si>
-    <t>25,995,782.8</t>
-  </si>
-  <si>
-    <t>8,231,146,859.1</t>
-  </si>
-  <si>
-    <t>54,174,719.7</t>
-  </si>
-  <si>
-    <t>38,737,055.6</t>
-  </si>
-  <si>
-    <t>34,120,454.7</t>
-  </si>
-  <si>
-    <t>17,451,801.0</t>
-  </si>
-  <si>
-    <t>163,998,390.9</t>
-  </si>
-  <si>
-    <t>95,310,371.1</t>
-  </si>
-  <si>
-    <t>71,949,757.7</t>
-  </si>
-  <si>
-    <t>65,875,822.1</t>
-  </si>
-  <si>
-    <t>37,396,267.0</t>
-  </si>
-  <si>
-    <t>240,974,724.1</t>
-  </si>
-  <si>
-    <t>163,429,698.1</t>
-  </si>
-  <si>
-    <t>66,411,379.7</t>
-  </si>
-  <si>
-    <t>37,434,674.0</t>
-  </si>
-  <si>
-    <t>137,759,678.4</t>
-  </si>
-  <si>
-    <t>59,955,597.6</t>
-  </si>
-  <si>
-    <t>55,018,946.6</t>
-  </si>
-  <si>
-    <t>47,793,415.9</t>
-  </si>
-  <si>
-    <t>46,904,905.2</t>
-  </si>
-  <si>
-    <t>60,549,354.8</t>
-  </si>
-  <si>
-    <t>54,250,908.2</t>
-  </si>
-  <si>
-    <t>50,767,148.0</t>
-  </si>
-  <si>
-    <t>48,764,680.4</t>
-  </si>
-  <si>
-    <t>31,504,961.5</t>
-  </si>
-  <si>
-    <t>97,895,167.9</t>
-  </si>
-  <si>
-    <t>68,398,723.59</t>
-  </si>
-  <si>
-    <t>36,706,437.79</t>
-  </si>
-  <si>
-    <t>23,833,737.1</t>
-  </si>
-  <si>
-    <t>21,489,855.8</t>
-  </si>
-  <si>
-    <t>67,262,430.0</t>
-  </si>
-  <si>
-    <t>38,356,045.6</t>
-  </si>
-  <si>
-    <t>29,481,206.3</t>
-  </si>
-  <si>
-    <t>15,734,774.9</t>
-  </si>
-  <si>
-    <t>10,466,886.5</t>
+    <t>263,601,472.3</t>
+  </si>
+  <si>
+    <t>100,985,637.2</t>
+  </si>
+  <si>
+    <t>44,869,814.9</t>
+  </si>
+  <si>
+    <t>34,030,836.6</t>
+  </si>
+  <si>
+    <t>22,852,321.1</t>
+  </si>
+  <si>
+    <t>188,593,878.1</t>
+  </si>
+  <si>
+    <t>155,920,733.8</t>
+  </si>
+  <si>
+    <t>47,971,481.7</t>
+  </si>
+  <si>
+    <t>37,959,625.6</t>
+  </si>
+  <si>
+    <t>23,675,276.9</t>
+  </si>
+  <si>
+    <t>91,184,543.3</t>
+  </si>
+  <si>
+    <t>70,492,170.25</t>
+  </si>
+  <si>
+    <t>31,746,553.5</t>
+  </si>
+  <si>
+    <t>27,202,965.8</t>
+  </si>
+  <si>
+    <t>17,809,371.2</t>
+  </si>
+  <si>
+    <t>83,541,340.6</t>
+  </si>
+  <si>
+    <t>71,648,658.5</t>
+  </si>
+  <si>
+    <t>55,706,345.1</t>
+  </si>
+  <si>
+    <t>27,770,545.0</t>
+  </si>
+  <si>
+    <t>13,236,026.3</t>
+  </si>
+  <si>
+    <t>193,642,375.4</t>
+  </si>
+  <si>
+    <t>155,443,190.3</t>
+  </si>
+  <si>
+    <t>44,213,797.4</t>
+  </si>
+  <si>
+    <t>13,888,015.4</t>
+  </si>
+  <si>
+    <t>10,328,813.0</t>
+  </si>
+  <si>
+    <t>92,135,992.6</t>
+  </si>
+  <si>
+    <t>78,144,318.5</t>
+  </si>
+  <si>
+    <t>36,318,595.2</t>
+  </si>
+  <si>
+    <t>26,729,851.2</t>
+  </si>
+  <si>
+    <t>19,367,386.7</t>
+  </si>
+  <si>
+    <t>73,073,666.59</t>
+  </si>
+  <si>
+    <t>70,061,500.4</t>
+  </si>
+  <si>
+    <t>62,239,561.1</t>
+  </si>
+  <si>
+    <t>35,141,433.9</t>
+  </si>
+  <si>
+    <t>21,907,778.7</t>
+  </si>
+  <si>
+    <t>287,408,699.6</t>
+  </si>
+  <si>
+    <t>106,227,359.2</t>
+  </si>
+  <si>
+    <t>76,703,309.8</t>
+  </si>
+  <si>
+    <t>42,256,999.2</t>
+  </si>
+  <si>
+    <t>31,260,556.5</t>
+  </si>
+  <si>
+    <t>94,618,059.5</t>
+  </si>
+  <si>
+    <t>81,002,721.8</t>
+  </si>
+  <si>
+    <t>61,090,490.2</t>
+  </si>
+  <si>
+    <t>23,891,389.5</t>
+  </si>
+  <si>
+    <t>21,604,871.5</t>
+  </si>
+  <si>
+    <t>79,978,805.2</t>
+  </si>
+  <si>
+    <t>66,905,419.1</t>
+  </si>
+  <si>
+    <t>42,266,861.5</t>
+  </si>
+  <si>
+    <t>40,767,594.4</t>
+  </si>
+  <si>
+    <t>35,590,529.29</t>
+  </si>
+  <si>
+    <t>103,565,474.5</t>
+  </si>
+  <si>
+    <t>51,076,623.0</t>
+  </si>
+  <si>
+    <t>30,509,486.0</t>
+  </si>
+  <si>
+    <t>26,768,640.8</t>
+  </si>
+  <si>
+    <t>22,580,968.0</t>
+  </si>
+  <si>
+    <t>35,833,350.7</t>
+  </si>
+  <si>
+    <t>34,235,874.29</t>
+  </si>
+  <si>
+    <t>29,661,297.0</t>
+  </si>
+  <si>
+    <t>14,361,822.8</t>
+  </si>
+  <si>
+    <t>5,046,220.5</t>
+  </si>
+  <si>
+    <t>73,792,070.59</t>
+  </si>
+  <si>
+    <t>73,591,149.8</t>
+  </si>
+  <si>
+    <t>31,999,159.2</t>
+  </si>
+  <si>
+    <t>22,907,968.0</t>
+  </si>
+  <si>
+    <t>12,613,382.9</t>
+  </si>
+  <si>
+    <t>76,953,668.3</t>
+  </si>
+  <si>
+    <t>48,774,302.5</t>
+  </si>
+  <si>
+    <t>20,528,958.8</t>
+  </si>
+  <si>
+    <t>17,829,979.39</t>
+  </si>
+  <si>
+    <t>15,684,224.6</t>
   </si>
 </sst>
 </file>
@@ -1687,61 +1687,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.4849575176417595</v>
+        <v>0.2048053379983346</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.1153019464109565</v>
+        <v>0.1313583666681559</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.02666975170618886</v>
+        <v>0.02879361258400591</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.05310385705161911</v>
+        <v>0.06176997131317086</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P9" s="18">
-        <v>0.09095460702556535</v>
+        <v>0.2903567784274839</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S9" s="16">
-        <v>0.05905767654986882</v>
+        <v>0.02453605124961503</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V9" s="18">
-        <v>0.08615425543245424</v>
+        <v>0.1207598322881972</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1753,61 +1753,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.002325966714938458</v>
+        <v>0.02909177549192917</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.09380175921286925</v>
+        <v>0.07207843636523437</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02388713411595633</v>
+        <v>0.02502261374810302</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02175728908771684</v>
+        <v>0.05280589691942623</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01702759244706408</v>
+        <v>0.2639136261491383</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03117919143787275</v>
+        <v>0.02029525995989538</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="V10" s="18">
-        <v>0.04055302617926311</v>
+        <v>0.02620841888059018</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1819,61 +1819,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.001677769183483749</v>
+        <v>0.02559602402939846</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.03362972649773982</v>
+        <v>0.03573178333653047</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01721173071674362</v>
+        <v>0.01696470669892407</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01630855407490436</v>
+        <v>0.02698071097100989</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01576829355068104</v>
+        <v>0.01966095774507801</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S11" s="16">
-        <v>0.0308917744135415</v>
+        <v>0.01575219463688565</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V11" s="18">
-        <v>0.034949594492035</v>
+        <v>0.0201255634605804</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1885,61 +1885,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.001612900141927977</v>
+        <v>0.02158645157422583</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.02687658793056592</v>
+        <v>0.01735444064639084</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01615443813753316</v>
+        <v>0.0158000790567304</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01584183386359916</v>
+        <v>0.02002558327040958</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01544370403879797</v>
+        <v>0.01468923281028141</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03070869600875836</v>
+        <v>0.01568152897500375</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03472144883320693</v>
+        <v>0.0164610246582395</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1951,61 +1951,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.001442366873585821</v>
+        <v>0.017047811148019</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.01564764367283561</v>
+        <v>0.01508776762154729</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01308874681960787</v>
+        <v>0.0104038013035095</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01087708881335207</v>
+        <v>0.01851884010240155</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>54</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01394285574489389</v>
+        <v>0.00981252118198511</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02294628669689389</v>
+        <v>0.01508461148946209</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03126420583579071</v>
+        <v>0.01645212346234102</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2016,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2025,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2034,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2043,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2052,7 +2052,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2061,7 +2061,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2070,7 +2070,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2082,103 +2082,103 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D16" s="10">
-        <v>0.4855029294715551</v>
+        <v>0.2159164536912303</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12">
-        <v>0.06986409819692957</v>
+        <v>0.05544324106869374</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2625033804081279</v>
+        <v>0.0363175901951306</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M16" s="16">
-        <v>0.08447232389553273</v>
+        <v>0.04537189003046359</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>151</v>
       </c>
       <c r="P16" s="18">
-        <v>0.02893669795778339</v>
+        <v>0.04183654977814102</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R16" s="15" t="s">
         <v>159</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1505490132559174</v>
+        <v>0.04468509738233317</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="U16" s="17" t="s">
         <v>167</v>
       </c>
       <c r="V16" s="18">
-        <v>0.01951631114528957</v>
+        <v>0.02756391659587462</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" s="10">
-        <v>0.001859976107158595</v>
+        <v>0.03374433490094782</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>129</v>
-      </c>
       <c r="G17" s="12">
-        <v>0.03159434617820996</v>
+        <v>0.02402620232166814</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08929926032044493</v>
+        <v>0.03293605774125027</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M17" s="16">
-        <v>0.06320580312126589</v>
+        <v>0.03307061728493751</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>152</v>
@@ -2187,25 +2187,25 @@
         <v>153</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02357864984402748</v>
+        <v>0.02351394929280086</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06129425515285543</v>
+        <v>0.01712653116517899</v>
       </c>
       <c r="T17" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="U17" s="17" t="s">
-        <v>169</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.01764515442468041</v>
+        <v>0.01582053096128406</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2214,169 +2214,169 @@
         <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D18" s="10">
-        <v>0.001517148254841337</v>
+        <v>0.03277622547530141</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>130</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03017253711314515</v>
+        <v>0.01727738942427697</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05539352588697178</v>
+        <v>0.02727647393078287</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05587738424967019</v>
+        <v>0.02434100248846954</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02221168500104173</v>
+        <v>0.02189117312474842</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S18" s="16">
-        <v>0.0206743196829075</v>
+        <v>0.01397625933365797</v>
       </c>
       <c r="T18" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="U18" s="17" t="s">
-        <v>171</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.01310890535395265</v>
+        <v>0.01571839784544824</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D19" s="10">
-        <v>0.001443413950263377</v>
+        <v>0.02774784077849886</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>131</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03001767018149587</v>
+        <v>0.0106971105868278</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J19" s="14">
-        <v>0.04269968767911794</v>
+        <v>0.02200722803225351</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03851345646982642</v>
+        <v>0.01905998108459269</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="O19" s="17" t="s">
         <v>156</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02106621000384933</v>
+        <v>0.01835993667541206</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0164184180220318</v>
+        <v>0.01262243494499047</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>172</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01182575301201267</v>
+        <v>0.01359458917304612</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D20" s="10">
-        <v>0.00082179078662895</v>
+        <v>0.02424275260350596</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02352490546684552</v>
+        <v>0.01020676044825867</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02926001743814593</v>
+        <v>0.0209180165978369</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03674289470728706</v>
+        <v>0.01885830210271574</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>157</v>
@@ -2385,33 +2385,33 @@
         <v>158</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0190826601271727</v>
+        <v>0.01616668990198636</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S20" s="16">
-        <v>0.012872431539566</v>
+        <v>0.01140136632121285</v>
       </c>
       <c r="T20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="U20" s="17" t="s">
-        <v>174</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01060587623002658</v>
+        <v>0.01315360046915794</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>175</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2419,226 +2419,226 @@
         <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>178</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>187</v>
-      </c>
       <c r="D31" s="22">
-        <v>1.166933661936984</v>
+        <v>0.2716596218431705</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>189</v>
-      </c>
       <c r="D32" s="22">
-        <v>0.2054098521043989</v>
+        <v>0.2320988485201664</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>191</v>
-      </c>
       <c r="D33" s="22">
-        <v>0.09326745739590991</v>
+        <v>0.1097911482511306</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>193</v>
-      </c>
       <c r="D34" s="22">
-        <v>0.08809545697033729</v>
+        <v>0.07144626399893114</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>195</v>
-      </c>
       <c r="D35" s="22">
-        <v>0.07416701427402039</v>
+        <v>0.06435693530928245</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>197</v>
-      </c>
       <c r="D36" s="22">
-        <v>0.07206589829241741</v>
+        <v>0.06070264504543087</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>199</v>
-      </c>
       <c r="D37" s="22">
-        <v>0.06146843399143596</v>
+        <v>0.04440321101253227</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="D38" s="22">
-        <v>0.03729540619830182</v>
+        <v>0.03367022981662478</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>203</v>
-      </c>
       <c r="D39" s="22">
-        <v>0.01891405391934876</v>
+        <v>0.03101844794460667</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>205</v>
-      </c>
       <c r="D40" s="22">
-        <v>0.01886280260191415</v>
+        <v>0.02272292035993203</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="C41" s="21" t="s">
-        <v>207</v>
-      </c>
       <c r="D41" s="22">
-        <v>0.00798047756446079</v>
+        <v>0.007496244778237452</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>209</v>
-      </c>
       <c r="D42" s="22">
-        <v>0.004789405387850703</v>
+        <v>0.006294000696583916</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="21" t="s">
-        <v>211</v>
-      </c>
       <c r="D43" s="22">
-        <v>0.004547435247886233</v>
+        <v>0.002601932878319007</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="C44" s="21" t="s">
-        <v>213</v>
-      </c>
       <c r="D44" s="22">
-        <v>0.001436600113272354</v>
+        <v>0.001929205014883008</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="C45" s="21" t="s">
-        <v>215</v>
-      </c>
       <c r="D45" s="22">
-        <v>0.001159365286183118</v>
+        <v>0.0001999997471859164</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="D46" s="20" t="s">
         <v>217</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3017,331 +3017,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D9" s="10">
-        <v>0.4859888748615651</v>
+        <v>0.2335099148449241</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1688452240362907</v>
+        <v>0.2209757708823163</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J9" s="14">
-        <v>0.05844145864690296</v>
+        <v>0.1374676653093957</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M9" s="16">
-        <v>0.09296624227517666</v>
+        <v>0.1427443748043471</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1079090783730176</v>
+        <v>0.3400850714477963</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1930586726515658</v>
+        <v>0.1629847825707613</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V9" s="18">
-        <v>0.2556394567982025</v>
+        <v>0.1356417787056005</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" s="10">
-        <v>0.007537980050113493</v>
+        <v>0.08945757145201043</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1584890862040635</v>
+        <v>0.1826925915894373</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J10" s="14">
-        <v>0.05554597136548739</v>
+        <v>0.1062723320878873</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M10" s="16">
-        <v>0.06853467113791145</v>
+        <v>0.122423735239325</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1066552131644594</v>
+        <v>0.272997624461329</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="S10" s="16">
-        <v>0.06131304512868225</v>
+        <v>0.1382340863809484</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1341094112965717</v>
+        <v>0.1300504952770379</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D11" s="10">
-        <v>0.0021215070429138</v>
+        <v>0.03974767881600525</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06315643881634775</v>
+        <v>0.05620826749956116</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0545790519048946</v>
+        <v>0.04786035476327077</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0627713955513818</v>
+        <v>0.0951836222261282</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P11" s="18">
-        <v>0.08933790576193501</v>
+        <v>0.07765063001678808</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="S11" s="16">
-        <v>0.06122257428213565</v>
+        <v>0.06424610160381011</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07761662901506766</v>
+        <v>0.1155311504987475</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" s="10">
-        <v>0.0017948574373112</v>
+        <v>0.03014602948622274</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03770433902041613</v>
+        <v>0.04447735851169237</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0279144586071093</v>
+        <v>0.04101054918610683</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0310307860747891</v>
+        <v>0.04745062810257306</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03849166733088587</v>
+        <v>0.02439087363920601</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05734183144787019</v>
+        <v>0.04728400772643115</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04878114134678957</v>
+        <v>0.06523070241641997</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D13" s="10">
-        <v>0.001146032483060694</v>
+        <v>0.0202436029947389</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G13" s="12">
-        <v>0.03668500939199042</v>
+        <v>0.02774036260633953</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02323780601821077</v>
+        <v>0.02684898767807275</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02677604845944992</v>
+        <v>0.02261596816040795</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03534403226510868</v>
+        <v>0.01814001248342426</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S13" s="16">
-        <v>0.04894371733110786</v>
+        <v>0.03426011074702803</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V13" s="18">
-        <v>0.04737799661016708</v>
+        <v>0.04066594997378534</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3352,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3361,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3370,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3379,7 +3379,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3388,7 +3388,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3397,7 +3397,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3406,7 +3406,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3415,331 +3415,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D16" s="10">
-        <v>0.4874797457973696</v>
+        <v>0.2545994162464561</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1576812727910046</v>
+        <v>0.1108641428239519</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2651944705575158</v>
+        <v>0.1205741590316103</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>268</v>
       </c>
       <c r="M16" s="16">
-        <v>0.2084896485543409</v>
+        <v>0.1769589619060776</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>273</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1005474357761351</v>
+        <v>0.06293244238432039</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R16" s="15" t="s">
         <v>278</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1759832993765815</v>
+        <v>0.1305351387964237</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U16" s="17" t="s">
         <v>283</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1225875444893931</v>
+        <v>0.1428439673524304</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D17" s="10">
-        <v>0.003208432438403528</v>
+        <v>0.09410092206451293</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09163907366868548</v>
+        <v>0.09491102825633452</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1798555944938797</v>
+        <v>0.1008650307099104</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>269</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09073860811575098</v>
+        <v>0.08727296647250997</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>274</v>
       </c>
       <c r="P17" s="18">
-        <v>0.09008832094172044</v>
+        <v>0.06012686909744069</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R17" s="15" t="s">
         <v>279</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1229583983610988</v>
+        <v>0.1301797181624472</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U17" s="17" t="s">
         <v>284</v>
       </c>
       <c r="V17" s="18">
-        <v>0.06990490005233517</v>
+        <v>0.09053648809549428</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D18" s="10">
-        <v>0.002294155400222238</v>
+        <v>0.06794720523919408</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G18" s="12">
-        <v>0.06917829686547482</v>
+        <v>0.07157983229108639</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07308621576106476</v>
+        <v>0.06372052280005863</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>270</v>
       </c>
       <c r="M18" s="16">
-        <v>0.08326733173082124</v>
+        <v>0.05213056761351494</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O18" s="17" t="s">
         <v>275</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08430323609439262</v>
+        <v>0.05209275236704881</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R18" s="15" t="s">
         <v>280</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06598609687256349</v>
+        <v>0.05660519692126459</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="U18" s="17" t="s">
         <v>285</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05373027244038353</v>
+        <v>0.03810653845862978</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D19" s="10">
-        <v>0.002020742779635612</v>
+        <v>0.03743313039452256</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G19" s="12">
-        <v>0.06333832556452107</v>
+        <v>0.02799358211093585</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="J19" s="14">
-        <v>0.04269968767911794</v>
+        <v>0.0614602631063284</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>271</v>
       </c>
       <c r="M19" s="16">
-        <v>0.07233199583458412</v>
+        <v>0.04573870694335181</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="O19" s="17" t="s">
         <v>276</v>
       </c>
       <c r="P19" s="18">
-        <v>0.08097796560935037</v>
+        <v>0.02522299947503427</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R19" s="15" t="s">
         <v>281</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04284521678962295</v>
+        <v>0.0405232534892988</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>286</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02867704033417074</v>
+        <v>0.03309660282053255</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D20" s="10">
-        <v>0.00103356186699316</v>
+        <v>0.0276919920918057</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03595578557711472</v>
+        <v>0.02531446504321015</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>267</v>
       </c>
       <c r="J20" s="14">
-        <v>0.04119713629303084</v>
+        <v>0.05365544195248101</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L20" s="15" t="s">
         <v>272</v>
       </c>
       <c r="M20" s="16">
-        <v>0.07098729696673477</v>
+        <v>0.03858336646846876</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>277</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0523167109462058</v>
+        <v>0.008862441682709466</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="R20" s="15" t="s">
         <v>282</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03863168946882174</v>
+        <v>0.02231255572795836</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>287</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01907617542934708</v>
+        <v>0.02911358114828927</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-15.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
   <si>
     <t>Date: 2024-07-15</t>
   </si>
@@ -68,18 +68,18 @@
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>44</t>
   </si>
   <si>
@@ -89,79 +89,79 @@
     <t>34</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
-    <t>1,128,866,294.5</t>
-  </si>
-  <si>
-    <t>853,459,532.45</t>
-  </si>
-  <si>
-    <t>663,316,301.29</t>
-  </si>
-  <si>
-    <t>585,251,367.79</t>
-  </si>
-  <si>
-    <t>569,393,930.1</t>
-  </si>
-  <si>
-    <t>565,304,264.28</t>
-  </si>
-  <si>
-    <t>538,725,363.95</t>
-  </si>
-  <si>
-    <t>515,851,077.0</t>
-  </si>
-  <si>
-    <t>513,931,585.7</t>
-  </si>
-  <si>
-    <t>296,574,446.1</t>
-  </si>
-  <si>
-    <t>294,696,364.1</t>
-  </si>
-  <si>
-    <t>440,711,608.1</t>
-  </si>
-  <si>
-    <t>312,144,762.88</t>
-  </si>
-  <si>
-    <t>315,711,535.7</t>
-  </si>
-  <si>
-    <t>613,015,217.5</t>
-  </si>
-  <si>
-    <t>339,527,946.75</t>
-  </si>
-  <si>
-    <t>366,741,855.19</t>
-  </si>
-  <si>
-    <t>290,555,003.7</t>
-  </si>
-  <si>
-    <t>128,682,322.0</t>
-  </si>
-  <si>
-    <t>253,159,501.4</t>
-  </si>
-  <si>
-    <t>223,013,828.25</t>
+    <t>57</t>
+  </si>
+  <si>
+    <t>1,195,503,253.59</t>
+  </si>
+  <si>
+    <t>885,076,979.1</t>
+  </si>
+  <si>
+    <t>749,625,617.39</t>
+  </si>
+  <si>
+    <t>638,764,325.78</t>
+  </si>
+  <si>
+    <t>570,439,823.4</t>
+  </si>
+  <si>
+    <t>567,710,911.54</t>
+  </si>
+  <si>
+    <t>542,195,622.49</t>
+  </si>
+  <si>
+    <t>577,329,251.7</t>
+  </si>
+  <si>
+    <t>470,283,368.3</t>
+  </si>
+  <si>
+    <t>343,330,358.6</t>
+  </si>
+  <si>
+    <t>344,403,521.08</t>
+  </si>
+  <si>
+    <t>313,951,472.3</t>
+  </si>
+  <si>
+    <t>301,669,668.5</t>
+  </si>
+  <si>
+    <t>291,085,998.49</t>
+  </si>
+  <si>
+    <t>618,174,001.9</t>
+  </si>
+  <si>
+    <t>414,793,610.8</t>
+  </si>
+  <si>
+    <t>406,295,258.79</t>
+  </si>
+  <si>
+    <t>294,360,804.7</t>
+  </si>
+  <si>
+    <t>256,488,351.1</t>
+  </si>
+  <si>
+    <t>266,041,243.05</t>
+  </si>
+  <si>
+    <t>251,109,624.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,13 +182,13 @@
     <t>UPPER</t>
   </si>
   <si>
-    <t>231,197,843.0</t>
+    <t>231,223,418.0</t>
   </si>
   <si>
     <t>SPIL</t>
   </si>
   <si>
-    <t>32,840,724.79</t>
+    <t>54,986,326.4</t>
   </si>
   <si>
     <t>SBI</t>
@@ -200,244 +200,232 @@
     <t>MSLB</t>
   </si>
   <si>
-    <t>24,368,217.6</t>
+    <t>24,507,817.6</t>
   </si>
   <si>
     <t>LSL</t>
   </si>
   <si>
-    <t>19,244,699.39</t>
-  </si>
-  <si>
-    <t>112,109,050.2</t>
+    <t>22,008,115.4</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>61,516,028.6</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>30,495,631.1</t>
+    <t>62,723,684.6</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>22,091,063.9</t>
+  </si>
+  <si>
+    <t>21,367,400.2</t>
   </si>
   <si>
     <t>LBBL</t>
   </si>
   <si>
-    <t>14,811,312.8</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>12,876,799.1</t>
+    <t>15,954,171.8</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>15,156,688.3</t>
   </si>
   <si>
     <t>AHPC</t>
   </si>
   <si>
-    <t>19,099,272.6</t>
-  </si>
-  <si>
-    <t>16,597,907.6</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>11,252,966.5</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>10,480,450.0</t>
+    <t>20,551,701.7</t>
+  </si>
+  <si>
+    <t>10,501,951.69</t>
   </si>
   <si>
     <t>CHDC</t>
   </si>
   <si>
-    <t>6,901,011.0</t>
+    <t>8,067,911.0</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>7,686,185.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>7,481,412.1</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>10,099,255.69</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>8,363,586.5</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>7,995,951.0</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>6,852,783.5</t>
+  </si>
+  <si>
+    <t>6,527,473.9</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>28,335,136.3</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>16,038,216.0</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>11,930,742.3</t>
+  </si>
+  <si>
+    <t>GBILD84/85</t>
+  </si>
+  <si>
+    <t>11,720,000.0</t>
   </si>
   <si>
     <t>NMB</t>
   </si>
   <si>
-    <t>36,150,960.2</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>30,904,723.4</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>15,790,498.0</t>
-  </si>
-  <si>
-    <t>GBILD84/85</t>
-  </si>
-  <si>
-    <t>11,720,000.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>10,838,176.5</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>165,327,387.19</t>
+    <t>11,173,105.8</t>
+  </si>
+  <si>
+    <t>NICL</t>
+  </si>
+  <si>
+    <t>18,738,120.6</t>
+  </si>
+  <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>12,753,386.5</t>
+  </si>
+  <si>
+    <t>8,674,995.69</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>8,673,942.0</t>
+  </si>
+  <si>
+    <t>8,305,442.2</t>
+  </si>
+  <si>
+    <t>15,280,522.5</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>9,915,216.5</t>
+  </si>
+  <si>
+    <t>8,873,504.69</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>7,698,625.2</t>
+  </si>
+  <si>
+    <t>ACLBSL</t>
+  </si>
+  <si>
+    <t>7,419,631.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>244,472,087.0</t>
+  </si>
+  <si>
+    <t>39,697,732.4</t>
+  </si>
+  <si>
+    <t>35,151,602.2</t>
+  </si>
+  <si>
+    <t>24,372,196.6</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>22,585,506.3</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>52,862,938.1</t>
+  </si>
+  <si>
+    <t>SIFC</t>
+  </si>
+  <si>
+    <t>17,139,152.7</t>
+  </si>
+  <si>
+    <t>12,125,774.4</t>
   </si>
   <si>
     <t>NIFRA</t>
   </si>
   <si>
-    <t>150,270,816.8</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>11,194,830.0</t>
-  </si>
-  <si>
-    <t>8,363,960.0</t>
-  </si>
-  <si>
-    <t>5,587,190.0</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>13,870,334.39</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>11,472,997.0</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>8,904,782.8</t>
-  </si>
-  <si>
-    <t>KPCL</t>
-  </si>
-  <si>
-    <t>8,864,835.19</t>
-  </si>
-  <si>
-    <t>8,527,395.19</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>65,056,384.6</t>
-  </si>
-  <si>
-    <t>MHNL</t>
-  </si>
-  <si>
-    <t>14,119,140.0</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>10,842,151.5</t>
+    <t>9,569,871.0</t>
+  </si>
+  <si>
+    <t>9,530,941.3</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>26,405,676.1</t>
+  </si>
+  <si>
+    <t>18,660,846.2</t>
   </si>
   <si>
     <t>EBL</t>
   </si>
   <si>
-    <t>8,867,971.5</t>
-  </si>
-  <si>
-    <t>8,863,176.19</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>243,740,807.0</t>
-  </si>
-  <si>
-    <t>38,092,842.29</t>
-  </si>
-  <si>
-    <t>36,999,976.2</t>
-  </si>
-  <si>
-    <t>31,323,602.2</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>27,366,826.3</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>47,318,562.6</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>20,505,391.39</t>
-  </si>
-  <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>14,745,552.7</t>
-  </si>
-  <si>
-    <t>9,129,551.0</t>
-  </si>
-  <si>
-    <t>NWCL</t>
-  </si>
-  <si>
-    <t>8,711,057.0</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>24,090,049.6</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>21,847,024.0</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>18,092,929.8</t>
-  </si>
-  <si>
-    <t>14,597,753.1</t>
+    <t>17,535,349.1</t>
   </si>
   <si>
     <t>MERO</t>
@@ -446,97 +434,85 @@
     <t>13,875,261.4</t>
   </si>
   <si>
-    <t>26,553,960.7</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>19,354,624.0</t>
-  </si>
-  <si>
-    <t>SLBSL</t>
-  </si>
-  <si>
-    <t>14,245,605.0</t>
-  </si>
-  <si>
-    <t>11,154,880.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>11,036,847.1</t>
-  </si>
-  <si>
-    <t>23,821,477.5</t>
-  </si>
-  <si>
-    <t>PRVUPO</t>
-  </si>
-  <si>
-    <t>13,388,700.0</t>
-  </si>
-  <si>
-    <t>UNL</t>
-  </si>
-  <si>
-    <t>12,464,701.1</t>
-  </si>
-  <si>
-    <t>10,454,036.5</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>9,205,215.1</t>
-  </si>
-  <si>
-    <t>25,260,676.1</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>9,681,701.1</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>7,900,839.0</t>
-  </si>
-  <si>
-    <t>7,135,516.3</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>6,445,241.0</t>
-  </si>
-  <si>
-    <t>14,849,381.0</t>
-  </si>
-  <si>
-    <t>8,522,921.3</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>8,467,899.6</t>
-  </si>
-  <si>
-    <t>VLBS</t>
+    <t>13,513,328.7</t>
+  </si>
+  <si>
+    <t>10,322,881.1</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>10,134,089.4</t>
+  </si>
+  <si>
+    <t>NLICL</t>
+  </si>
+  <si>
+    <t>9,892,601.5</t>
+  </si>
+  <si>
+    <t>9,452,384.9</t>
+  </si>
+  <si>
+    <t>9,446,502.3</t>
+  </si>
+  <si>
+    <t>12,951,085.5</t>
+  </si>
+  <si>
+    <t>12,437,653.1</t>
+  </si>
+  <si>
+    <t>11,121,453.5</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>7,518,058.5</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>6,362,364.0</t>
+  </si>
+  <si>
+    <t>15,707,521.0</t>
+  </si>
+  <si>
+    <t>8,899,314.5</t>
   </si>
   <si>
     <t>7,323,750.0</t>
   </si>
   <si>
-    <t>7,086,178.2</t>
+    <t>5,518,742.4</t>
+  </si>
+  <si>
+    <t>5,039,481.59</t>
+  </si>
+  <si>
+    <t>11,017,906.0</t>
+  </si>
+  <si>
+    <t>NHPC</t>
+  </si>
+  <si>
+    <t>10,519,148.0</t>
+  </si>
+  <si>
+    <t>8,880,594.19</t>
+  </si>
+  <si>
+    <t>6,375,577.0</t>
+  </si>
+  <si>
+    <t>ALBSL</t>
+  </si>
+  <si>
+    <t>5,302,493.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -554,112 +530,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>354,523,738.9</t>
-  </si>
-  <si>
-    <t>253,124,714.5</t>
-  </si>
-  <si>
-    <t>224,284,500.0</t>
-  </si>
-  <si>
-    <t>189,862,991.6</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>155,864,343.5</t>
+    <t>370,872,589.6</t>
+  </si>
+  <si>
+    <t>219,897,603.5</t>
+  </si>
+  <si>
+    <t>191,546,122.6</t>
+  </si>
+  <si>
+    <t>177,860,072.5</t>
+  </si>
+  <si>
+    <t>166,252,878.3</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,371,978,612.0</t>
+    <t>2,337,328,298.6</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>2,026,556,250.15</t>
+    <t>2,055,063,382.45</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>958,634,388.4</t>
+    <t>1,019,536,208.5</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>623,828,484.2</t>
+    <t>702,995,693.9</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>561,928,464.2</t>
+    <t>633,773,703.79</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>530,021,262.5</t>
+    <t>629,643,797.4</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>387,703,796.8</t>
+    <t>494,486,453.8</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>293,989,458.0</t>
+    <t>256,429,689.9</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>226,659,817.4</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>270,835,594.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>198,403,725.7</t>
+    <t>165,393,484.8</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>65,452,981.8</t>
+    <t>105,426,701.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>54,955,664.5</t>
+    <t>60,193,504.4</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>22,718,610.5</t>
+    <t>28,398,889.5</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>16,844,730.19</t>
+    <t>14,100,745.9</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>1,746,285.0</t>
+    <t>2,005,665.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -671,214 +644,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>263,601,472.3</t>
-  </si>
-  <si>
-    <t>100,985,637.2</t>
-  </si>
-  <si>
-    <t>44,869,814.9</t>
-  </si>
-  <si>
-    <t>34,030,836.6</t>
-  </si>
-  <si>
-    <t>22,852,321.1</t>
-  </si>
-  <si>
-    <t>188,593,878.1</t>
-  </si>
-  <si>
-    <t>155,920,733.8</t>
-  </si>
-  <si>
-    <t>47,971,481.7</t>
-  </si>
-  <si>
-    <t>37,959,625.6</t>
-  </si>
-  <si>
-    <t>23,675,276.9</t>
-  </si>
-  <si>
-    <t>91,184,543.3</t>
-  </si>
-  <si>
-    <t>70,492,170.25</t>
-  </si>
-  <si>
-    <t>31,746,553.5</t>
-  </si>
-  <si>
-    <t>27,202,965.8</t>
-  </si>
-  <si>
-    <t>17,809,371.2</t>
-  </si>
-  <si>
-    <t>83,541,340.6</t>
-  </si>
-  <si>
-    <t>71,648,658.5</t>
-  </si>
-  <si>
-    <t>55,706,345.1</t>
-  </si>
-  <si>
-    <t>27,770,545.0</t>
-  </si>
-  <si>
-    <t>13,236,026.3</t>
-  </si>
-  <si>
-    <t>193,642,375.4</t>
-  </si>
-  <si>
-    <t>155,443,190.3</t>
-  </si>
-  <si>
-    <t>44,213,797.4</t>
-  </si>
-  <si>
-    <t>13,888,015.4</t>
-  </si>
-  <si>
-    <t>10,328,813.0</t>
-  </si>
-  <si>
-    <t>92,135,992.6</t>
-  </si>
-  <si>
-    <t>78,144,318.5</t>
-  </si>
-  <si>
-    <t>36,318,595.2</t>
-  </si>
-  <si>
-    <t>26,729,851.2</t>
-  </si>
-  <si>
-    <t>19,367,386.7</t>
-  </si>
-  <si>
-    <t>73,073,666.59</t>
-  </si>
-  <si>
-    <t>70,061,500.4</t>
-  </si>
-  <si>
-    <t>62,239,561.1</t>
-  </si>
-  <si>
-    <t>35,141,433.9</t>
-  </si>
-  <si>
-    <t>21,907,778.7</t>
-  </si>
-  <si>
-    <t>287,408,699.6</t>
-  </si>
-  <si>
-    <t>106,227,359.2</t>
-  </si>
-  <si>
-    <t>76,703,309.8</t>
-  </si>
-  <si>
-    <t>42,256,999.2</t>
-  </si>
-  <si>
-    <t>31,260,556.5</t>
-  </si>
-  <si>
-    <t>94,618,059.5</t>
-  </si>
-  <si>
-    <t>81,002,721.8</t>
-  </si>
-  <si>
-    <t>61,090,490.2</t>
-  </si>
-  <si>
-    <t>23,891,389.5</t>
-  </si>
-  <si>
-    <t>21,604,871.5</t>
-  </si>
-  <si>
-    <t>79,978,805.2</t>
-  </si>
-  <si>
-    <t>66,905,419.1</t>
-  </si>
-  <si>
-    <t>42,266,861.5</t>
-  </si>
-  <si>
-    <t>40,767,594.4</t>
-  </si>
-  <si>
-    <t>35,590,529.29</t>
-  </si>
-  <si>
-    <t>103,565,474.5</t>
-  </si>
-  <si>
-    <t>51,076,623.0</t>
-  </si>
-  <si>
-    <t>30,509,486.0</t>
-  </si>
-  <si>
-    <t>26,768,640.8</t>
-  </si>
-  <si>
-    <t>22,580,968.0</t>
-  </si>
-  <si>
-    <t>35,833,350.7</t>
-  </si>
-  <si>
-    <t>34,235,874.29</t>
-  </si>
-  <si>
-    <t>29,661,297.0</t>
-  </si>
-  <si>
-    <t>14,361,822.8</t>
-  </si>
-  <si>
-    <t>5,046,220.5</t>
-  </si>
-  <si>
-    <t>73,792,070.59</t>
-  </si>
-  <si>
-    <t>73,591,149.8</t>
-  </si>
-  <si>
-    <t>31,999,159.2</t>
-  </si>
-  <si>
-    <t>22,907,968.0</t>
-  </si>
-  <si>
-    <t>12,613,382.9</t>
-  </si>
-  <si>
-    <t>76,953,668.3</t>
-  </si>
-  <si>
-    <t>48,774,302.5</t>
-  </si>
-  <si>
-    <t>20,528,958.8</t>
-  </si>
-  <si>
-    <t>17,829,979.39</t>
-  </si>
-  <si>
-    <t>15,684,224.6</t>
+    <t>273,468,635.89</t>
+  </si>
+  <si>
+    <t>134,746,479.4</t>
+  </si>
+  <si>
+    <t>47,539,492.9</t>
+  </si>
+  <si>
+    <t>36,080,444.19</t>
+  </si>
+  <si>
+    <t>27,122,727.6</t>
+  </si>
+  <si>
+    <t>148,717,884.3</t>
+  </si>
+  <si>
+    <t>115,045,797.3</t>
+  </si>
+  <si>
+    <t>56,787,776.8</t>
+  </si>
+  <si>
+    <t>46,092,262.9</t>
+  </si>
+  <si>
+    <t>28,939,558.8</t>
+  </si>
+  <si>
+    <t>99,998,633.2</t>
+  </si>
+  <si>
+    <t>89,803,841.95</t>
+  </si>
+  <si>
+    <t>26,816,055.5</t>
+  </si>
+  <si>
+    <t>23,890,730.7</t>
+  </si>
+  <si>
+    <t>23,047,919.4</t>
+  </si>
+  <si>
+    <t>94,277,953.9</t>
+  </si>
+  <si>
+    <t>86,760,068.9</t>
+  </si>
+  <si>
+    <t>43,051,968.7</t>
+  </si>
+  <si>
+    <t>33,719,372.1</t>
+  </si>
+  <si>
+    <t>24,847,193.7</t>
+  </si>
+  <si>
+    <t>86,276,561.7</t>
+  </si>
+  <si>
+    <t>60,751,855.7</t>
+  </si>
+  <si>
+    <t>41,698,785.79</t>
+  </si>
+  <si>
+    <t>31,833,911.0</t>
+  </si>
+  <si>
+    <t>28,943,740.8</t>
+  </si>
+  <si>
+    <t>77,122,667.4</t>
+  </si>
+  <si>
+    <t>72,000,235.9</t>
+  </si>
+  <si>
+    <t>39,457,339.29</t>
+  </si>
+  <si>
+    <t>23,905,518.1</t>
+  </si>
+  <si>
+    <t>23,323,259.6</t>
+  </si>
+  <si>
+    <t>72,383,129.0</t>
+  </si>
+  <si>
+    <t>67,175,707.8</t>
+  </si>
+  <si>
+    <t>35,983,717.9</t>
+  </si>
+  <si>
+    <t>29,247,019.8</t>
+  </si>
+  <si>
+    <t>24,048,534.2</t>
+  </si>
+  <si>
+    <t>302,007,262.1</t>
+  </si>
+  <si>
+    <t>100,718,604.1</t>
+  </si>
+  <si>
+    <t>55,488,798.7</t>
+  </si>
+  <si>
+    <t>43,389,780.5</t>
+  </si>
+  <si>
+    <t>27,788,612.5</t>
+  </si>
+  <si>
+    <t>95,969,858.4</t>
+  </si>
+  <si>
+    <t>93,966,712.7</t>
+  </si>
+  <si>
+    <t>87,735,192.5</t>
+  </si>
+  <si>
+    <t>33,861,009.0</t>
+  </si>
+  <si>
+    <t>30,003,717.6</t>
+  </si>
+  <si>
+    <t>91,112,058.9</t>
+  </si>
+  <si>
+    <t>76,926,191.59</t>
+  </si>
+  <si>
+    <t>62,337,683.5</t>
+  </si>
+  <si>
+    <t>40,129,050.2</t>
+  </si>
+  <si>
+    <t>36,128,282.29</t>
+  </si>
+  <si>
+    <t>80,247,353.2</t>
+  </si>
+  <si>
+    <t>70,227,602.8</t>
+  </si>
+  <si>
+    <t>36,897,234.7</t>
+  </si>
+  <si>
+    <t>31,421,089.9</t>
+  </si>
+  <si>
+    <t>21,044,460.1</t>
+  </si>
+  <si>
+    <t>68,032,449.8</t>
+  </si>
+  <si>
+    <t>56,769,148.4</t>
+  </si>
+  <si>
+    <t>29,543,712.0</t>
+  </si>
+  <si>
+    <t>23,986,510.6</t>
+  </si>
+  <si>
+    <t>19,897,640.39</t>
+  </si>
+  <si>
+    <t>94,000,033.9</t>
+  </si>
+  <si>
+    <t>52,755,625.8</t>
+  </si>
+  <si>
+    <t>25,030,383.8</t>
+  </si>
+  <si>
+    <t>21,450,402.8</t>
+  </si>
+  <si>
+    <t>20,613,369.2</t>
+  </si>
+  <si>
+    <t>64,446,570.0</t>
+  </si>
+  <si>
+    <t>51,419,769.1</t>
+  </si>
+  <si>
+    <t>28,788,993.7</t>
+  </si>
+  <si>
+    <t>26,573,173.3</t>
+  </si>
+  <si>
+    <t>25,522,603.5</t>
   </si>
 </sst>
 </file>
@@ -1687,16 +1660,16 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2048053379983346</v>
+        <v>0.1934109483213204</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1313583666681559</v>
+        <v>0.07086805563938772</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>73</v>
@@ -1705,7 +1678,7 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.02879361258400591</v>
+        <v>0.02741595434205629</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>82</v>
@@ -1714,34 +1687,34 @@
         <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.06176997131317086</v>
+        <v>0.01581061322995413</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>93</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.2903567784274839</v>
+        <v>0.04967243719260993</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S9" s="16">
-        <v>0.02453605124961503</v>
+        <v>0.03300644785713209</v>
       </c>
       <c r="T9" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="U9" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="U9" s="17" t="s">
-        <v>110</v>
-      </c>
       <c r="V9" s="18">
-        <v>0.1207598322881972</v>
+        <v>0.02818267405005068</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1753,16 +1726,16 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02909177549192917</v>
+        <v>0.04599429255790024</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.07207843636523437</v>
+        <v>0.0249594830976889</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>54</v>
@@ -1771,7 +1744,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02502261374810302</v>
+        <v>0.01400959553192038</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>84</v>
@@ -1780,34 +1753,34 @@
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.05280589691942623</v>
+        <v>0.01309338383884723</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.2639136261491383</v>
+        <v>0.02811552655003504</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02029525995989538</v>
+        <v>0.02246457878567087</v>
       </c>
       <c r="T10" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="U10" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="U10" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="V10" s="18">
-        <v>0.02620841888059018</v>
+        <v>0.01828715704945197</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1819,16 +1792,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02559602402939846</v>
+        <v>0.02416931004829179</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03573178333653047</v>
+        <v>0.02414185512058812</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1837,7 +1810,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01696470669892407</v>
+        <v>0.01076258710059876</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>86</v>
@@ -1846,34 +1819,34 @@
         <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02698071097100989</v>
+        <v>0.01251784214817583</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.01966095774507801</v>
+        <v>0.0209149884187416</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="R11" s="15" t="s">
         <v>105</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01575219463688565</v>
+        <v>0.01528065697436567</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0201255634605804</v>
+        <v>0.0163658730021629</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1885,7 +1858,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02158645157422583</v>
+        <v>0.0205000007538248</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
@@ -1894,7 +1867,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01735444064639084</v>
+        <v>0.01802574485241179</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1903,7 +1876,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0158000790567304</v>
+        <v>0.01025336490868773</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>88</v>
@@ -1912,16 +1885,16 @@
         <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02002558327040958</v>
+        <v>0.01072818757001186</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="O12" s="17" t="s">
         <v>98</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01468923281028141</v>
+        <v>0.02054555015136414</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>106</v>
@@ -1930,16 +1903,16 @@
         <v>107</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01568152897500375</v>
+        <v>0.01527880092407923</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0164610246582395</v>
+        <v>0.01419898073806745</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1951,7 +1924,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.017047811148019</v>
+        <v>0.01840908030465606</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1960,7 +1933,7 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01508776762154729</v>
+        <v>0.01712471192665325</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>80</v>
@@ -1969,43 +1942,43 @@
         <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0104038013035095</v>
+        <v>0.009980198016775781</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.01851884010240155</v>
+        <v>0.01021890803314548</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P13" s="18">
-        <v>0.00981252118198511</v>
+        <v>0.0195868264130032</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="R13" s="15" t="s">
         <v>108</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01508461148946209</v>
+        <v>0.01462970330678331</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01645212346234102</v>
+        <v>0.01368441701156826</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2016,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2025,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2034,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2043,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2052,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2061,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2070,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2082,336 +2055,336 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2159164536912303</v>
+        <v>0.2044930335938653</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>126</v>
-      </c>
       <c r="G16" s="12">
-        <v>0.05544324106869374</v>
+        <v>0.05972693827575794</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0363175901951306</v>
+        <v>0.03522515171231427</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M16" s="16">
-        <v>0.04537189003046359</v>
+        <v>0.01616070385176043</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P16" s="18">
-        <v>0.04183654977814102</v>
+        <v>0.02270368401491936</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="R16" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.02766816821807131</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="S16" s="16">
-        <v>0.04468509738233317</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>167</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.02756391659587462</v>
+        <v>0.0203209054868443</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="10">
-        <v>0.03374433490094782</v>
+        <v>0.03320587566822495</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>128</v>
-      </c>
       <c r="G17" s="12">
-        <v>0.02402620232166814</v>
+        <v>0.01936458986587599</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J17" s="14">
-        <v>0.03293605774125027</v>
+        <v>0.02489355455190042</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M17" s="16">
-        <v>0.03307061728493751</v>
+        <v>0.01586514617519566</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02351394929280086</v>
+        <v>0.02180361992588051</v>
       </c>
       <c r="Q17" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.01567578554321342</v>
+      </c>
+      <c r="T17" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="R17" s="15" t="s">
+      <c r="U17" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="S17" s="16">
-        <v>0.01712653116517899</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>168</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.01582053096128406</v>
+        <v>0.01940101978634844</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03277622547530141</v>
+        <v>0.02940318405169417</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.01370024832453582</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.02339214228170789</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.01548709140561359</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.0194962782116309</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.01290049187183005</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.01727738942427697</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.02727647393078287</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.02434100248846954</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.02189117312474842</v>
-      </c>
-      <c r="Q18" s="15" t="s">
+      <c r="U18" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="R18" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.01397625933365797</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>170</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.01571839784544824</v>
+        <v>0.01637894854114907</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02774784077849886</v>
+        <v>0.02038655815164735</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0106971105868278</v>
+        <v>0.01081247306842307</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02200722803225351</v>
+        <v>0.01850958809053247</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01905998108459269</v>
+        <v>0.01479792236120516</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01835993667541206</v>
+        <v>0.01317940682189756</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01262243494499047</v>
+        <v>0.009721043382682893</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01359458917304612</v>
+        <v>0.01175881312121362</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="D20" s="10">
-        <v>0.02424275260350596</v>
+        <v>0.01889204921190187</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01020676044825867</v>
+        <v>0.01076848853270553</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J20" s="14">
-        <v>0.0209180165978369</v>
+        <v>0.01802677014567601</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="L20" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01478871301784865</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.0111534358910609</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.01885830210271574</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="O20" s="17" t="s">
+      <c r="R20" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.01616668990198636</v>
-      </c>
-      <c r="Q20" s="15" t="s">
+      <c r="S20" s="16">
+        <v>0.008876844706473742</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01140136632121285</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>173</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01315360046915794</v>
+        <v>0.009779669145332867</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2419,226 +2392,226 @@
         <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2716596218431705</v>
+        <v>0.2676911665681651</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2320988485201664</v>
+        <v>0.2353637332629177</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1097911482511306</v>
+        <v>0.1167661544060035</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07144626399893114</v>
+        <v>0.08051318144105223</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D35" s="22">
-        <v>0.06435693530928245</v>
+        <v>0.07258527704989842</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06070264504543087</v>
+        <v>0.07211228424751996</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04440321101253227</v>
+        <v>0.05663288967543119</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03367022981662478</v>
+        <v>0.02936855848327332</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03101844794460667</v>
+        <v>0.0259590537496491</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02272292035993203</v>
+        <v>0.01894230045278847</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D41" s="22">
-        <v>0.007496244778237452</v>
+        <v>0.01207438287945267</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D42" s="22">
-        <v>0.006294000696583916</v>
+        <v>0.006893883680060442</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002601932878319007</v>
+        <v>0.003252487835811896</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001929205014883008</v>
+        <v>0.001614940067132712</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0001999997471859164</v>
+        <v>0.0002297062008432994</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3017,331 +2990,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2335099148449241</v>
+        <v>0.2287477136314838</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2209757708823163</v>
+        <v>0.1680281916847791</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1374676653093957</v>
+        <v>0.1333981001718818</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1427443748043471</v>
+        <v>0.1475942692711846</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="P9" s="18">
-        <v>0.3400850714477963</v>
+        <v>0.1512456847521</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1629847825707613</v>
+        <v>0.1358484852606318</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1356417787056005</v>
+        <v>0.133500024709873</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10">
-        <v>0.08945757145201043</v>
+        <v>0.1127110938378796</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1826925915894373</v>
+        <v>0.1299839449185375</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1062723320878873</v>
+        <v>0.1197982564452285</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="M10" s="16">
-        <v>0.122423735239325</v>
+        <v>0.1358248502592198</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="P10" s="18">
-        <v>0.272997624461329</v>
+        <v>0.1065000254328317</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1382340863809484</v>
+        <v>0.1268255276324009</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1300504952770379</v>
+        <v>0.1238957029780132</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03974767881600525</v>
+        <v>0.03976525597638073</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05620826749956116</v>
+        <v>0.06416139854608495</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04786035476327077</v>
+        <v>0.0357725975179003</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0951836222261282</v>
+        <v>0.06739883077757812</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="P11" s="18">
-        <v>0.07765063001678808</v>
+        <v>0.07309935963352308</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16">
-        <v>0.06424610160381011</v>
+        <v>0.0695025205562301</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="V11" s="18">
-        <v>0.1155311504987475</v>
+        <v>0.06636666990180959</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03014602948622274</v>
+        <v>0.03018013049429312</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04447735851169237</v>
+        <v>0.05207712322025301</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04101054918610683</v>
+        <v>0.03187021647309928</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04745062810257306</v>
+        <v>0.05278843970947347</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02439087363920601</v>
+        <v>0.05580590571369987</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04728400772643115</v>
+        <v>0.04210861129079174</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="V12" s="18">
-        <v>0.06523070241641997</v>
+        <v>0.05394182207832085</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D13" s="10">
-        <v>0.0202436029947389</v>
+        <v>0.02268728882027361</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02774036260633953</v>
+        <v>0.03269722236977342</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02684898767807275</v>
+        <v>0.03074590684380133</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02261596816040795</v>
+        <v>0.03889884374751033</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01814001248342426</v>
+        <v>0.05073934114116761</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03426011074702803</v>
+        <v>0.04108298629723599</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="V13" s="18">
-        <v>0.04066594997378534</v>
+        <v>0.0443539807451019</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3352,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3361,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3370,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3379,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3388,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3397,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3406,7 +3379,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3415,331 +3388,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2545994162464561</v>
+        <v>0.2526193560666358</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1108641428239519</v>
+        <v>0.108431086409668</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1205741590316103</v>
+        <v>0.1215434168555076</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1769589619060776</v>
+        <v>0.125629046521985</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="P16" s="18">
-        <v>0.06293244238432039</v>
+        <v>0.11926314925649</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1305351387964237</v>
+        <v>0.1655772894048403</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1428439673524304</v>
+        <v>0.1188622101079184</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09410092206451293</v>
+        <v>0.08424787117618264</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09491102825633452</v>
+        <v>0.1061678418023606</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1008650307099104</v>
+        <v>0.1026194807320444</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08727296647250997</v>
+        <v>0.109942900637484</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="P17" s="18">
-        <v>0.06012686909744069</v>
+        <v>0.09951820695413251</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1301797181624472</v>
+        <v>0.09292691883614369</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09053648809549428</v>
+        <v>0.09483619374103</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D18" s="10">
-        <v>0.06794720523919408</v>
+        <v>0.04641459446714801</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07157983229108639</v>
+        <v>0.09912718844999727</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06372052280005863</v>
+        <v>0.08315842208947377</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05213056761351494</v>
+        <v>0.05776345548875872</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05209275236704881</v>
+        <v>0.05179111062742819</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05660519692126459</v>
+        <v>0.04409001710335367</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03810653845862978</v>
+        <v>0.05309706037055098</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03743313039452256</v>
+        <v>0.03629415509271183</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02799358211093585</v>
+        <v>0.03825769938613919</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0614602631063284</v>
+        <v>0.05353212226086781</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04573870694335181</v>
+        <v>0.0491904269413159</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02522299947503427</v>
+        <v>0.04204915157751941</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0405232534892988</v>
+        <v>0.03778402416369762</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03309660282053255</v>
+        <v>0.04901030587071939</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0276919920918057</v>
+        <v>0.0232442801107572</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02531446504321015</v>
+        <v>0.03389955711028616</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J20" s="14">
-        <v>0.05365544195248101</v>
+        <v>0.04819510094357395</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03858336646846876</v>
+        <v>0.03294557828398205</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="P20" s="18">
-        <v>0.008862441682709466</v>
+        <v>0.03488122600102467</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02231255572795836</v>
+        <v>0.03630962305043615</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02911358114828927</v>
+        <v>0.0470726845465646</v>
       </c>
     </row>
   </sheetData>
